--- a/target/test-classes/TestOneData.xlsx
+++ b/target/test-classes/TestOneData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sabav\hybridProjects\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CBF97422-6E8F-4447-94C2-6097F39E972B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEC615A6-95ED-49E9-B543-BD678A3F10B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5F9BCBA9-F32B-46C8-BDC4-DE71F7EBEBB9}"/>
   </bookViews>
@@ -54,10 +54,10 @@
     <t>naikjai</t>
   </si>
   <si>
-    <t>nj@gmail.com</t>
-  </si>
-  <si>
-    <t>jnaik@gmail.com</t>
+    <t>hhhhhnj@gmail.com</t>
+  </si>
+  <si>
+    <t>kkkkjnaik@gmail.com</t>
   </si>
 </sst>
 </file>
